--- a/DSA_REVISION.xlsx
+++ b/DSA_REVISION.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="93">
   <si>
     <t>problem</t>
   </si>
@@ -89,6 +89,9 @@
     <t>73. Set Matrix Zeroes</t>
   </si>
   <si>
+    <t>done 22 jan</t>
+  </si>
+  <si>
     <t>54. Spiral Matrix</t>
   </si>
   <si>
@@ -299,12 +302,21 @@
     <t>875. Koko Eating Bananas</t>
   </si>
   <si>
+    <t>437. Path Sum III</t>
+  </si>
+  <si>
     <t>402. Remove K Digits</t>
   </si>
   <si>
     <t>21feb</t>
   </si>
   <si>
+    <t>692. Top K Frequent Words</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>105. Construct Binary Tree from Preorder and Inorder Traversal</t>
   </si>
   <si>
@@ -321,6 +333,12 @@
   </si>
   <si>
     <t>236. Lowest Common Ancestor of a Binary Tree</t>
+  </si>
+  <si>
+    <t>687. Longest Univalue Path</t>
+  </si>
+  <si>
+    <t>27mar</t>
   </si>
 </sst>
 </file>
@@ -368,6 +386,12 @@
     </font>
     <font>
       <sz val="18"/>
+      <color rgb="FF007AFF"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
@@ -387,12 +411,6 @@
     <font>
       <sz val="18"/>
       <color rgb="FF0A84FF"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF007AFF"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
@@ -541,12 +559,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -1045,14 +1063,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1062,9 +1080,6 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
       <extLst>
@@ -1082,50 +1097,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1140,7 +1158,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1660,14 +1678,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF40"/>
+  <dimension ref="A1:AF41"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.81818181818182"/>
     <col min="10" max="10" width="8.81818181818182"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1675,7 +1693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:27">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1686,7 +1704,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="43.5" spans="1:3">
+    <row r="3" ht="43.5" spans="1:27">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1697,7 +1715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="26" spans="1:8">
+    <row r="4" ht="26" spans="1:27">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1713,7 +1731,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="156" spans="1:3">
+    <row r="5" ht="156" spans="1:27">
       <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
@@ -1724,38 +1742,45 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" ht="26" spans="1:5">
+    <row r="6" ht="26" spans="1:27">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="9">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="2">
         <v>46002</v>
       </c>
-    </row>
-    <row r="7" ht="130" spans="1:2">
-      <c r="A7" s="10" t="s">
+      <c r="F6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="9">
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" ht="130" spans="1:27">
+      <c r="A7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="10">
         <v>46003</v>
       </c>
     </row>
-    <row r="8" ht="17" spans="1:21">
+    <row r="8" ht="17" spans="1:27">
       <c r="A8" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" ht="26" spans="1:24">
-      <c r="A9" s="12" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="9" ht="26" spans="1:27">
+      <c r="A9" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>3</v>
@@ -1764,61 +1789,61 @@
         <v>237</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="X9" s="1"/>
     </row>
-    <row r="10" ht="17" spans="1:24">
-      <c r="A10" s="13" t="s">
+    <row r="10" ht="17" spans="1:27">
+      <c r="A10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="13" t="s">
         <v>15</v>
-      </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>14</v>
       </c>
       <c r="U10" s="1">
         <v>118</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="X10" s="1"/>
     </row>
-    <row r="11" ht="156" spans="1:24">
-      <c r="A11" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="14" t="s">
+    <row r="11" ht="156" spans="1:27">
+      <c r="A11" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="16"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="12" t="s">
-        <v>18</v>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="V11" s="1"/>
       <c r="W11" s="2">
@@ -1830,29 +1855,29 @@
     </row>
     <row r="12" ht="156" spans="1:27">
       <c r="A12" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="12" t="s">
         <v>21</v>
+      </c>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
@@ -1865,66 +1890,66 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" ht="26" spans="1:25">
+    <row r="13" ht="26" spans="1:27">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="14" t="s">
         <v>24</v>
       </c>
+      <c r="C13" s="13" t="s">
+        <v>25</v>
+      </c>
       <c r="D13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="12" t="s">
-        <v>25</v>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="2"/>
       <c r="Y13" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" ht="26" spans="1:25">
-      <c r="A14" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="14" t="s">
+    </row>
+    <row r="14" ht="26" spans="1:27">
+      <c r="A14" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>6</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
     </row>
-    <row r="15" ht="26" spans="1:25">
-      <c r="A15" s="12" t="s">
-        <v>30</v>
+    <row r="15" ht="26" spans="1:27">
+      <c r="A15" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1938,28 +1963,28 @@
       <c r="I15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="28"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="28"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
       <c r="U15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
     </row>
-    <row r="16" ht="26" spans="1:25">
-      <c r="A16" s="12" t="s">
-        <v>32</v>
+    <row r="16" ht="26" spans="1:27">
+      <c r="A16" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1973,19 +1998,19 @@
       <c r="I16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
-      <c r="U16" s="12" t="s">
-        <v>33</v>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
@@ -1996,60 +2021,60 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" ht="182" spans="1:24">
-      <c r="A17" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="19">
+    <row r="17" ht="182" spans="1:32">
+      <c r="A17" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="21">
         <v>46021</v>
       </c>
-      <c r="F17" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="20"/>
-      <c r="U17" s="29" t="s">
+      <c r="F17" s="13" t="s">
         <v>36</v>
       </c>
+      <c r="G17" s="22"/>
+      <c r="U17" s="23" t="s">
+        <v>37</v>
+      </c>
       <c r="V17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="X17" s="16"/>
-    </row>
-    <row r="18" ht="26" spans="1:28">
+      <c r="X17" s="15"/>
+    </row>
+    <row r="18" ht="26" spans="1:32">
       <c r="A18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I18" s="14"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="28"/>
-      <c r="O18" s="28"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="12" t="s">
+      <c r="H18" s="13" t="s">
         <v>41</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
@@ -2063,12 +2088,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" ht="26" spans="1:29">
-      <c r="A19" s="12">
+    <row r="19" ht="26" spans="1:32">
+      <c r="A19" s="8">
         <v>1390</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="2">
@@ -2077,8 +2102,8 @@
       <c r="E19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U19" s="12" t="s">
-        <v>43</v>
+      <c r="U19" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
@@ -2087,15 +2112,15 @@
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC19" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:32">
       <c r="A20" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="2">
@@ -2105,7 +2130,7 @@
         <v>3</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V20" s="2"/>
       <c r="W20" s="2">
@@ -2115,20 +2140,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
-      <c r="A21" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="19">
+    <row r="21" spans="1:32">
+      <c r="A21" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="21">
         <v>46046</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="13" t="s">
         <v>6</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V21" s="2">
         <v>46071</v>
@@ -2137,12 +2162,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" ht="26" spans="1:26">
+    <row r="22" ht="26" spans="1:32">
       <c r="A22" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="U22" s="12" t="s">
         <v>50</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
@@ -2154,74 +2190,94 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" ht="182" spans="1:23">
-      <c r="A23" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="9">
+    <row r="23" ht="182" spans="1:32">
+      <c r="A23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="2">
         <v>46052</v>
       </c>
-      <c r="U23" s="30" t="s">
-        <v>52</v>
+      <c r="D23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="24" t="s">
+        <v>53</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" ht="208" spans="1:22">
-      <c r="A24" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="9">
+    <row r="24" ht="208" spans="1:32">
+      <c r="A24" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="10">
         <v>46054</v>
       </c>
-      <c r="U24" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="V24" s="9">
+      <c r="U24" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="V24" s="2">
         <v>46074</v>
       </c>
-    </row>
-    <row r="25" ht="156" spans="1:29">
-      <c r="A25" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="9">
+      <c r="W24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" ht="156" spans="1:32">
+      <c r="A25" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="10">
         <v>46054</v>
       </c>
       <c r="U25" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC25" s="9">
+        <v>58</v>
+      </c>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="2">
         <v>46076</v>
       </c>
-    </row>
-    <row r="26" ht="182" spans="1:26">
-      <c r="A26" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="AD25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" ht="182" spans="1:32">
+      <c r="A26" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="U26" s="12" t="s">
+      <c r="B26" s="1" t="s">
         <v>60</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z26" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" ht="78" spans="1:24">
-      <c r="A27" s="22" t="s">
-        <v>62</v>
+    <row r="27" ht="78" spans="1:32">
+      <c r="A27" s="25" t="s">
+        <v>63</v>
       </c>
       <c r="B27" s="2">
         <v>46065</v>
@@ -2230,7 +2286,7 @@
         <v>3</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V27" s="1"/>
       <c r="W27" s="2">
@@ -2240,133 +2296,183 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:32">
       <c r="A28" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="U28" t="s">
-        <v>66</v>
-      </c>
-      <c r="W28" s="9">
+        <v>67</v>
+      </c>
+      <c r="W28" s="10">
         <v>46083</v>
       </c>
     </row>
     <row r="29" ht="26" spans="1:32">
-      <c r="A29" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="9">
+      <c r="A29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="10">
         <v>46068</v>
       </c>
-      <c r="U29" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF29" s="9">
+      <c r="U29" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF29" s="10">
         <v>46082</v>
       </c>
     </row>
-    <row r="30" ht="26" spans="1:28">
+    <row r="30" ht="26" spans="1:32">
       <c r="A30" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" t="s">
         <v>70</v>
       </c>
-      <c r="U30" s="25" t="s">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AB30" s="9">
+      <c r="G30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U30" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB30" s="10">
         <v>46087</v>
       </c>
     </row>
-    <row r="31" ht="208" spans="1:26">
-      <c r="A31" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="9">
+    <row r="31" ht="208" spans="1:32">
+      <c r="A31" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="10">
         <v>46070</v>
       </c>
-      <c r="U31" s="8" t="s">
-        <v>73</v>
+      <c r="U31" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="Z31" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" ht="260" spans="1:22">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" ht="260" spans="1:32">
       <c r="A32" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F32" s="9">
+        <v>76</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="2">
         <v>46072</v>
       </c>
-      <c r="U32" s="31" t="s">
-        <v>76</v>
+      <c r="G32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="27" t="s">
+        <v>77</v>
       </c>
       <c r="V32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" ht="26" spans="1:6">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" ht="26" spans="1:24">
       <c r="A33" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F33" s="9">
+        <v>79</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="2">
         <v>46074</v>
       </c>
-    </row>
-    <row r="34" ht="26" spans="1:5">
+      <c r="G33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="X33" s="10">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="34" ht="182" spans="1:24">
       <c r="A34" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E34" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" ht="364" spans="1:3">
-      <c r="A35" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="19">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U34" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="V34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" ht="364" spans="1:24">
+      <c r="A35" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="21">
         <v>46082</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="13" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="36" ht="26" spans="1:6">
-      <c r="A36" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F36" s="9">
+      <c r="U35" s="30"/>
+    </row>
+    <row r="36" ht="26" spans="1:24">
+      <c r="A36" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F36" s="10">
         <v>46082</v>
       </c>
-    </row>
-    <row r="37" ht="26" spans="1:7">
-      <c r="A37" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="G37" s="9">
+      <c r="U36" s="30"/>
+    </row>
+    <row r="37" ht="26" spans="1:24">
+      <c r="A37" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="G37" s="10">
         <v>46084</v>
       </c>
-    </row>
-    <row r="38" ht="26" spans="1:7">
+      <c r="U37" s="30"/>
+    </row>
+    <row r="38" ht="26" spans="1:24">
       <c r="A38" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G38" s="9">
+        <v>88</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2">
         <v>46091</v>
       </c>
-    </row>
-    <row r="39" ht="26" spans="1:6">
-      <c r="A39" s="26" t="s">
-        <v>85</v>
+      <c r="H38" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" ht="26" spans="1:24">
+      <c r="A39" s="31" t="s">
+        <v>89</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2378,12 +2484,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" ht="26" spans="1:9">
-      <c r="A40" s="8" t="s">
-        <v>86</v>
+    <row r="40" ht="26" spans="1:24">
+      <c r="A40" s="16" t="s">
+        <v>90</v>
       </c>
       <c r="I40" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" ht="26" spans="1:24">
+      <c r="A41" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F41" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2414,21 +2528,24 @@
     <hyperlink ref="U22" r:id="rId25" display="229. Majority Element II" tooltip="https://leetcode.com/problems/majority-element-ii/"/>
     <hyperlink ref="A32" r:id="rId26" display="1922. Count Good Numbers" tooltip="https://leetcode.com/problems/count-good-numbers/"/>
     <hyperlink ref="U23" r:id="rId27" display="11. Container With Most Water" tooltip="https://leetcode.com/problems/container-with-most-water/"/>
-    <hyperlink ref="A33" r:id="rId28" display="875. Koko Eating Bananas" tooltip="https://leetcode.com/problems/koko-eating-bananas/"/>
-    <hyperlink ref="A34" r:id="rId29" display="402. Remove K Digits" tooltip="https://leetcode.com/problems/remove-k-digits/"/>
-    <hyperlink ref="U24" r:id="rId30" display="451. Sort Characters By Frequency" tooltip="https://leetcode.com/problems/sort-characters-by-frequency/"/>
-    <hyperlink ref="U25" r:id="rId31" display="987. Vertical Order Traversal of a Binary Tree" tooltip="https://leetcode.com/problems/vertical-order-traversal-of-a-binary-tree/"/>
-    <hyperlink ref="U26" r:id="rId32" display="735. Asteroid Collision" tooltip="https://leetcode.com/problems/asteroid-collision/"/>
-    <hyperlink ref="A35" r:id="rId33" display="105. Construct Binary Tree from Preorder and Inorder Traversal" tooltip="https://leetcode.com/problems/construct-binary-tree-from-preorder-and-inorder-traversal/"/>
-    <hyperlink ref="A36" r:id="rId34" display="99. Recover Binary Search Tree" tooltip="https://leetcode.com/problems/recover-binary-search-tree/"/>
-    <hyperlink ref="U29" r:id="rId35" display="1689. Partitioning Into Minimum Number Of Deci-Binary Numbers" tooltip="https://leetcode.com/problems/partitioning-into-minimum-number-of-deci-binary-numbers/"/>
-    <hyperlink ref="A37" r:id="rId36" display="1545. Find Kth Bit in Nth Binary String" tooltip="https://leetcode.com/problems/find-kth-bit-in-nth-binary-string/"/>
-    <hyperlink ref="U30" r:id="rId37" display="1781. Sum of Beauty of All Substrings" tooltip="https://leetcode.com/problems/sum-of-beauty-of-all-substrings/"/>
-    <hyperlink ref="A38" r:id="rId38" display="238. Product of Array Except Self" tooltip="https://leetcode.com/problems/product-of-array-except-self/"/>
-    <hyperlink ref="U31" r:id="rId39" display="240. Search a 2D Matrix II" tooltip="https://leetcode.com/problems/search-a-2d-matrix-ii/"/>
-    <hyperlink ref="A39" r:id="rId40" display="162. Find Peak Element" tooltip="https://leetcode.com/problems/find-peak-element/"/>
-    <hyperlink ref="A40" r:id="rId41" display="236. Lowest Common Ancestor of a Binary Tree" tooltip="https://leetcode.com/problems/lowest-common-ancestor-of-a-binary-tree/"/>
-    <hyperlink ref="U32" r:id="rId42" display="1011. Capacity To Ship Packages Within D Days" tooltip="https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/"/>
+    <hyperlink ref="A34" r:id="rId28" display="402. Remove K Digits" tooltip="https://leetcode.com/problems/remove-k-digits/"/>
+    <hyperlink ref="U24" r:id="rId29" display="451. Sort Characters By Frequency" tooltip="https://leetcode.com/problems/sort-characters-by-frequency/"/>
+    <hyperlink ref="U25" r:id="rId30" display="987. Vertical Order Traversal of a Binary Tree" tooltip="https://leetcode.com/problems/vertical-order-traversal-of-a-binary-tree/"/>
+    <hyperlink ref="U26" r:id="rId31" display="735. Asteroid Collision" tooltip="https://leetcode.com/problems/asteroid-collision/"/>
+    <hyperlink ref="A35" r:id="rId32" display="105. Construct Binary Tree from Preorder and Inorder Traversal" tooltip="https://leetcode.com/problems/construct-binary-tree-from-preorder-and-inorder-traversal/"/>
+    <hyperlink ref="A36" r:id="rId33" display="99. Recover Binary Search Tree" tooltip="https://leetcode.com/problems/recover-binary-search-tree/"/>
+    <hyperlink ref="U29" r:id="rId34" display="1689. Partitioning Into Minimum Number Of Deci-Binary Numbers" tooltip="https://leetcode.com/problems/partitioning-into-minimum-number-of-deci-binary-numbers/"/>
+    <hyperlink ref="A37" r:id="rId35" display="1545. Find Kth Bit in Nth Binary String" tooltip="https://leetcode.com/problems/find-kth-bit-in-nth-binary-string/"/>
+    <hyperlink ref="U30" r:id="rId36" display="1781. Sum of Beauty of All Substrings" tooltip="https://leetcode.com/problems/sum-of-beauty-of-all-substrings/"/>
+    <hyperlink ref="A38" r:id="rId37" display="238. Product of Array Except Self" tooltip="https://leetcode.com/problems/product-of-array-except-self/"/>
+    <hyperlink ref="U31" r:id="rId38" display="240. Search a 2D Matrix II" tooltip="https://leetcode.com/problems/search-a-2d-matrix-ii/"/>
+    <hyperlink ref="A39" r:id="rId39" display="162. Find Peak Element" tooltip="https://leetcode.com/problems/find-peak-element/"/>
+    <hyperlink ref="A40" r:id="rId40" display="236. Lowest Common Ancestor of a Binary Tree" tooltip="https://leetcode.com/problems/lowest-common-ancestor-of-a-binary-tree/"/>
+    <hyperlink ref="U32" r:id="rId41" display="1011. Capacity To Ship Packages Within D Days" tooltip="https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/"/>
+    <hyperlink ref="A33" r:id="rId42" display="875. Koko Eating Bananas" tooltip="https://leetcode.com/problems/koko-eating-bananas/"/>
+    <hyperlink ref="U33" r:id="rId43" display="437. Path Sum III" tooltip="https://leetcode.com/problems/path-sum-iii/"/>
+    <hyperlink ref="A41" r:id="rId44" display="687. Longest Univalue Path" tooltip="https://leetcode.com/problems/longest-univalue-path/"/>
+    <hyperlink ref="U34" r:id="rId45" display="692. Top K Frequent Words" tooltip="https://leetcode.com/problems/top-k-frequent-words/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/DSA_REVISION.xlsx
+++ b/DSA_REVISION.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="98">
   <si>
     <t>problem</t>
   </si>
@@ -320,7 +320,16 @@
     <t>105. Construct Binary Tree from Preorder and Inorder Traversal</t>
   </si>
   <si>
-    <t>99. Recover Binary Search Tree</t>
+    <t>678. Valid Parenthesis String</t>
+  </si>
+  <si>
+    <t>99. Recover Binary Search Tree(after morris)</t>
+  </si>
+  <si>
+    <t>435. Non-overlapping Intervals</t>
+  </si>
+  <si>
+    <t>5may</t>
   </si>
   <si>
     <t>1545. Find Kth Bit in Nth Binary String</t>
@@ -339,6 +348,12 @@
   </si>
   <si>
     <t>27mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45,55.jump game 1 2 </t>
+  </si>
+  <si>
+    <t>3may</t>
   </si>
 </sst>
 </file>
@@ -1136,8 +1151,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -1678,7 +1693,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF41"/>
+  <dimension ref="A1:AF42"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.81818181818182"/>
@@ -2383,7 +2398,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" ht="26" spans="1:24">
+    <row r="33" ht="26" spans="1:27">
       <c r="A33" s="8" t="s">
         <v>79</v>
       </c>
@@ -2404,7 +2419,7 @@
         <v>46108</v>
       </c>
     </row>
-    <row r="34" ht="182" spans="1:24">
+    <row r="34" ht="182" spans="1:27">
       <c r="A34" s="8" t="s">
         <v>81</v>
       </c>
@@ -2424,39 +2439,52 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" ht="364" spans="1:24">
-      <c r="A35" s="29" t="s">
+    <row r="35" ht="364" spans="1:27">
+      <c r="A35" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="B35" s="21">
+      <c r="B35" s="2">
         <v>46082</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="U35" s="30"/>
-    </row>
-    <row r="36" ht="26" spans="1:24">
+      <c r="D35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z35" s="10">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="36" ht="26" spans="1:27">
       <c r="A36" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F36" s="10">
         <v>46082</v>
       </c>
-      <c r="U36" s="30"/>
-    </row>
-    <row r="37" ht="26" spans="1:24">
+      <c r="U36" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" ht="26" spans="1:27">
       <c r="A37" s="26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G37" s="10">
         <v>46084</v>
       </c>
       <c r="U37" s="30"/>
     </row>
-    <row r="38" ht="26" spans="1:24">
+    <row r="38" ht="26" spans="1:27">
       <c r="A38" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2470,9 +2498,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" ht="26" spans="1:24">
+    <row r="39" ht="26" spans="1:27">
       <c r="A39" s="31" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2484,20 +2512,28 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" ht="26" spans="1:24">
+    <row r="40" ht="26" spans="1:27">
       <c r="A40" s="16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I40" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="41" ht="26" spans="1:24">
+    <row r="41" ht="26" spans="1:27">
       <c r="A41" s="16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>92</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27">
+      <c r="A42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D42" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2533,7 +2569,7 @@
     <hyperlink ref="U25" r:id="rId30" display="987. Vertical Order Traversal of a Binary Tree" tooltip="https://leetcode.com/problems/vertical-order-traversal-of-a-binary-tree/"/>
     <hyperlink ref="U26" r:id="rId31" display="735. Asteroid Collision" tooltip="https://leetcode.com/problems/asteroid-collision/"/>
     <hyperlink ref="A35" r:id="rId32" display="105. Construct Binary Tree from Preorder and Inorder Traversal" tooltip="https://leetcode.com/problems/construct-binary-tree-from-preorder-and-inorder-traversal/"/>
-    <hyperlink ref="A36" r:id="rId33" display="99. Recover Binary Search Tree" tooltip="https://leetcode.com/problems/recover-binary-search-tree/"/>
+    <hyperlink ref="A36" r:id="rId33" display="99. Recover Binary Search Tree(after morris)" tooltip="https://leetcode.com/problems/recover-binary-search-tree/"/>
     <hyperlink ref="U29" r:id="rId34" display="1689. Partitioning Into Minimum Number Of Deci-Binary Numbers" tooltip="https://leetcode.com/problems/partitioning-into-minimum-number-of-deci-binary-numbers/"/>
     <hyperlink ref="A37" r:id="rId35" display="1545. Find Kth Bit in Nth Binary String" tooltip="https://leetcode.com/problems/find-kth-bit-in-nth-binary-string/"/>
     <hyperlink ref="U30" r:id="rId36" display="1781. Sum of Beauty of All Substrings" tooltip="https://leetcode.com/problems/sum-of-beauty-of-all-substrings/"/>
@@ -2546,6 +2582,8 @@
     <hyperlink ref="U33" r:id="rId43" display="437. Path Sum III" tooltip="https://leetcode.com/problems/path-sum-iii/"/>
     <hyperlink ref="A41" r:id="rId44" display="687. Longest Univalue Path" tooltip="https://leetcode.com/problems/longest-univalue-path/"/>
     <hyperlink ref="U34" r:id="rId45" display="692. Top K Frequent Words" tooltip="https://leetcode.com/problems/top-k-frequent-words/"/>
+    <hyperlink ref="U35" r:id="rId46" display="678. Valid Parenthesis String" tooltip="https://leetcode.com/problems/valid-parenthesis-string/"/>
+    <hyperlink ref="U36" r:id="rId47" display="435. Non-overlapping Intervals" tooltip="https://leetcode.com/problems/non-overlapping-intervals/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
